--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -12298,12 +12298,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -12328,90 +12328,104 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12438,17 +12452,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -12473,31 +12487,48 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="n">
-        <v>0</v>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Hepatit D</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -12505,6 +12536,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12517,12 +12606,12 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -12530,47 +12619,47 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12597,17 +12686,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12646,163 +12735,467 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr">
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
+      <c r="AT73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Hepatitis D</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA72" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
+      <c r="AB74" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
+      <c r="AC74" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD72" t="inlineStr">
+      <c r="AD74" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE72" t="inlineStr">
+      <c r="AE74" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF72" t="inlineStr">
+      <c r="AF74" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG72" t="inlineStr">
+      <c r="AG74" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH72" t="inlineStr">
+      <c r="AH74" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr">
+      <c r="AI74" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK74" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN72" t="b">
+      <c r="AN74" t="b">
         <v>1</v>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP72" t="inlineStr">
+      <c r="AP74" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ72" t="inlineStr">
+      <c r="AQ74" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="AT72" t="n">
+      <c r="AT74" t="n">
         <v>1</v>
       </c>
-      <c r="AU72" t="inlineStr">
+      <c r="AU74" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV72" t="inlineStr">
+      <c r="AV74" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW72" t="inlineStr">
+      <c r="AW74" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr">
+      <c r="AY74" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA72" t="inlineStr">
+      <c r="BA74" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB72" t="inlineStr">
+      <c r="BB74" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC72" t="inlineStr">
+      <c r="BC74" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -12924,7 +13317,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -12934,7 +13327,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -12954,7 +13347,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -12986,7 +13379,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -11905,12 +11905,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -11944,13 +11944,16 @@
         </is>
       </c>
       <c r="N68" t="n">
+        <v>25</v>
+      </c>
+      <c r="O68" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q68" t="n">
         <v>0</v>
       </c>
-      <c r="O68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>0.001769392789234687</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -11959,7 +11962,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_CN_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -11969,7 +11972,7 @@
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
@@ -11979,12 +11982,12 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_CN_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT68" t="n">
@@ -11992,47 +11995,47 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -12064,12 +12067,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -12103,29 +12106,29 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_CN_HEPATITIS_D</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_CN_HEPATITIS_D</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Hepatitis D</t>
+          <t>丁型肝炎</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -12135,7 +12138,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -12150,7 +12153,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -12165,7 +12168,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
@@ -12185,17 +12188,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
+          <t>China CDC source-reported hepatitis D component.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -12203,7 +12206,7 @@
       </c>
       <c r="AO69" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP69" t="inlineStr">
@@ -12213,12 +12216,12 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_CN_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT69" t="n">
@@ -12226,47 +12229,47 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -12298,12 +12301,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -12337,13 +12340,13 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0.02803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -12352,7 +12355,7 @@
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+          <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -12372,12 +12375,12 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+          <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
       <c r="AT70" t="n">
@@ -12385,47 +12388,47 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12457,12 +12460,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -12496,29 +12499,29 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+          <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+          <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Hepatit D</t>
+          <t>Hepatitis D</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
@@ -12543,7 +12546,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD71" t="inlineStr">
@@ -12578,17 +12581,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
         </is>
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -12606,12 +12609,12 @@
       </c>
       <c r="AQ71" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+          <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
       <c r="AT71" t="n">
@@ -12619,47 +12622,47 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12691,12 +12694,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12721,90 +12724,104 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12831,17 +12848,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -12866,31 +12883,48 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0</v>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Hepatit D</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -12898,6 +12932,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12910,12 +13002,12 @@
       </c>
       <c r="AQ73" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT73" t="n">
@@ -12923,47 +13015,47 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12990,17 +13082,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13039,163 +13131,467 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr">
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
+      <c r="AT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
         <is>
           <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Hepatitis D</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA74" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>country:FI:national</t>
         </is>
       </c>
-      <c r="AD74" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE74" t="inlineStr">
+      <c r="AE76" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF74" t="inlineStr">
+      <c r="AF76" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG74" t="inlineStr">
+      <c r="AG76" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH74" t="inlineStr">
+      <c r="AH76" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI74" t="inlineStr">
+      <c r="AI76" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AJ76" t="inlineStr">
         <is>
           <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
-      <c r="AK74" t="inlineStr">
+      <c r="AK76" t="inlineStr">
         <is>
           <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AM76" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN74" t="b">
+      <c r="AN76" t="b">
         <v>1</v>
       </c>
-      <c r="AO74" t="inlineStr">
+      <c r="AO76" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP74" t="inlineStr">
+      <c r="AP76" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ74" t="inlineStr">
+      <c r="AQ76" t="inlineStr">
         <is>
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="AT74" t="n">
+      <c r="AT76" t="n">
         <v>1</v>
       </c>
-      <c r="AU74" t="inlineStr">
+      <c r="AU76" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV74" t="inlineStr">
+      <c r="AV76" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW74" t="inlineStr">
+      <c r="AW76" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
+      <c r="AX76" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY74" t="inlineStr">
+      <c r="AY76" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA74" t="inlineStr">
+      <c r="BA76" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB74" t="inlineStr">
+      <c r="BB76" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC74" t="inlineStr">
+      <c r="BC76" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13317,7 +13713,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -13327,7 +13723,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
@@ -13347,7 +13743,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -13379,7 +13775,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -10006,7 +10006,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -12694,12 +12694,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -12733,95 +12733,81 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>0.02803464128485004</v>
+        <v>0</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV72" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12848,7 +12834,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -12897,98 +12883,23 @@
       <c r="O73" t="n">
         <v>3</v>
       </c>
+      <c r="R73" t="n">
+        <v>0.02803464128485004</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Hepatit D</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN73" t="b">
-        <v>1</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -13082,17 +12993,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13117,90 +13028,179 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
-      </c>
-      <c r="R74" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Hepatit D</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN74" t="b">
+        <v>1</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
+        </is>
+      </c>
       <c r="AT74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -13232,12 +13232,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13284,82 +13284,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1330</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1330</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13372,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -13435,98 +13421,23 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
+      <c r="R76" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1330</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Hepatitis D</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF76" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG76" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN76" t="b">
-        <v>1</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -13592,6 +13503,240 @@
         </is>
       </c>
       <c r="BC76" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN77" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA77" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB77" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC77" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -13713,7 +13858,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -13723,7 +13868,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -24191,13 +24191,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.02203687091711874</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -24657,6 +24657,399 @@
         </is>
       </c>
       <c r="BC133" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -24695,7 +25088,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -24778,7 +25171,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -24788,7 +25181,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -24808,7 +25201,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -24840,7 +25233,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1338,6 +1358,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1483,6 +1508,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1764,6 +1799,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1900,6 +1940,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2990,6 +3035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3531,6 +3581,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3667,6 +3722,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3803,6 +3863,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3948,6 +4013,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4093,6 +4163,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4229,6 +4304,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4374,6 +4454,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4519,6 +4604,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4655,6 +4745,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5745,6 +5840,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6286,6 +6386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6431,6 +6536,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6567,6 +6677,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6712,6 +6827,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6848,6 +6968,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6984,6 +7109,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7129,6 +7259,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7265,6 +7400,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7401,6 +7541,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8101,6 +8246,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8639,6 +8789,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8784,6 +8939,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8920,6 +9080,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9065,6 +9230,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9201,6 +9371,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9337,6 +9512,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9482,6 +9662,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9618,6 +9803,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9754,6 +9944,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10454,6 +10649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10992,6 +11192,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11137,6 +11342,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11273,6 +11483,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11418,6 +11633,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11554,6 +11774,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11699,6 +11924,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11844,6 +12074,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11980,6 +12215,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12116,6 +12356,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13596,6 +13841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14134,6 +14384,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14279,6 +14534,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14415,6 +14675,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14560,6 +14825,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14696,6 +14966,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14832,6 +15107,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14977,6 +15257,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15113,6 +15398,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15249,6 +15539,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19069,6 +19364,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19607,6 +19907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19743,6 +20048,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19879,6 +20189,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20024,6 +20339,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20160,6 +20480,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20305,6 +20630,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20450,6 +20780,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20586,6 +20921,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20722,6 +21062,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25166,6 +25511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25704,6 +26054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25849,6 +26204,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25985,6 +26345,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26130,6 +26495,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26266,6 +26636,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26411,6 +26786,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26556,6 +26936,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26692,6 +27077,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26828,6 +27218,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30492,6 +30887,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31017,17 +31417,22 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O180" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R180" t="n">
-        <v>0.02938249455615832</v>
+        <v>0.03305530637567811</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -31175,6 +31580,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31311,6 +31721,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31456,6 +31871,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31592,6 +32012,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31737,6 +32162,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31882,6 +32312,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32018,6 +32453,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32154,6 +32594,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32640,12 +33085,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -32670,22 +33115,22 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R191" t="n">
-        <v>0</v>
+        <v>0.02803464128485004</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -32694,7 +33139,7 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -32714,12 +33159,12 @@
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -32727,47 +33172,47 @@
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -32799,12 +33244,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -32829,38 +33274,38 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>Hepatitis D</t>
+          <t>Hepatit D</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -32885,7 +33330,7 @@
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD192" t="inlineStr">
@@ -32920,17 +33365,17 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -32948,12 +33393,12 @@
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1330</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_D</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -32961,45 +33406,438 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
-      <c r="AV192" t="inlineStr">
+      <c r="AV193" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW192" t="inlineStr">
+      <c r="AW193" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX192" t="inlineStr">
+      <c r="AX193" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY192" t="inlineStr">
+      <c r="AY193" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ192" t="inlineStr">
+      <c r="AZ193" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA192" t="inlineStr">
+      <c r="BA193" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB192" t="inlineStr">
+      <c r="BB193" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC192" t="inlineStr">
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X194" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD194" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE194" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF194" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG194" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH194" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI194" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1330.</t>
+        </is>
+      </c>
+      <c r="AM194" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN194" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1330</t>
+        </is>
+      </c>
+      <c r="AT194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -33121,7 +33959,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -33131,7 +33969,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
@@ -33151,7 +33989,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -33183,7 +34021,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -33517,13 +33517,13 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R193" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
@@ -33676,10 +33676,10 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U194" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d010/2026-2029.xlsx
+++ b/diseases/d010/2026-2029.xlsx
@@ -46873,13 +46873,13 @@
         </is>
       </c>
       <c r="N334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R334" t="n">
-        <v>0.01778809170864137</v>
+        <v>0</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
@@ -55639,117 +55639,252 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>丁型肝炎</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N397" t="n">
+        <v>6</v>
+      </c>
+      <c r="O397" t="n">
+        <v>6</v>
+      </c>
+      <c r="R397" t="n">
+        <v>0.02203687091711874</v>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO397" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP397" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS397" t="inlineStr"/>
+      <c r="AT397" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV397" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW397" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX397" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY397" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA397" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB397" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC397" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>hepatitis-d</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
           <t>FI</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr">
+      <c r="G398" t="inlineStr">
         <is>
           <t>Finland</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>D010</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>Hepatitis D</t>
-        </is>
-      </c>
-      <c r="J397" t="inlineStr">
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>D010</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Hepatitis D</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
         <is>
           <t>丁型肝炎</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr">
+      <c r="K398" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L397" t="inlineStr">
+      <c r="L398" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M397" t="inlineStr">
+      <c r="M398" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N397" t="n">
+      <c r="N398" t="n">
         <v>1</v>
       </c>
-      <c r="O397" t="n">
+      <c r="O398" t="n">
         <v>1</v>
       </c>
-      <c r="R397" t="n">
+      <c r="R398" t="n">
         <v>0.01778809170864137</v>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="U398" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="AA397" t="inlineStr">
+      <c r="AA398" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AO397" t="inlineStr">
+      <c r="AO398" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP397" t="inlineStr">
+      <c r="AP398" t="inlineStr">
         <is>
           <t>published_series</t>
         </is>
       </c>
-      <c r="AS397" t="inlineStr">
+      <c r="AS398" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1330</t>
         </is>
       </c>
-      <c r="AT397" t="n">
+      <c r="AT398" t="n">
         <v>1</v>
       </c>
-      <c r="AV397" t="inlineStr">
+      <c r="AV398" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="AW397" t="inlineStr">
+      <c r="AW398" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="AX397" t="inlineStr">
+      <c r="AX398" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="AY397" t="inlineStr">
+      <c r="AY398" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
       </c>
-      <c r="AZ397" t="inlineStr">
+      <c r="AZ398" t="inlineStr">
         <is>
           <t>thl_ttr</t>
         </is>
       </c>
-      <c r="BA397" t="inlineStr">
+      <c r="BA398" t="inlineStr">
         <is>
           <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
-      <c r="BB397" t="inlineStr">
+      <c r="BB398" t="inlineStr">
         <is>
           <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
-      <c r="BC397" t="inlineStr">
+      <c r="BC398" t="inlineStr">
         <is>
           <t>cube_csv</t>
         </is>
@@ -55871,7 +56006,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10">
@@ -55881,7 +56016,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11">
@@ -55933,7 +56068,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="16">
